--- a/aiDataWorks_Site_Page_Tracker.xlsx
+++ b/aiDataWorks_Site_Page_Tracker.xlsx
@@ -44,7 +44,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -63,22 +63,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCA5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,9 +123,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -525,7 +517,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rows 1-30: every HTML page that exists in the repo today, re-verified against index.html's actual nav/footer source. Rows 31-40: pages/content not built yet but called for (see Status + Notes). Generated 2026-08-11, updated 2026-08-12.</t>
+          <t>Rows 1-38: every real, live page in the repo today (38 total), including Partners/Blog/Whitepapers/Newsroom/Leadership &amp; Team/Trust/404/robots+sitemap, all built 2026-08-12. Rows 39-40: still-open content-parity gaps (see Notes). Generated 2026-08-11, updated 2026-08-12.</t>
         </is>
       </c>
     </row>
@@ -2321,53 +2313,53 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Partners Overview (proposed: partners.html)</t>
+          <t>Partners Overview</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>partners.html</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Missing (High Priority)</t>
+          <t>Partners | aiDataWorks</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Yes — but all 15 links alias to #partners anchor, not a real page</t>
+          <t>Yes — all 15 alliance/platform links now go to partners.html#technology-alliances / #cloud-platforms / #ai-platforms</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes — Partners column</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr"/>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>All 15 alliance/platform links in the Partners nav dropdown point to the same generic homepage logo-wall anchor. CAN BUILD NOW — no new content needed, partner names + 2 category groupings already exist in the nav dropdown itself. Follow the same one-pager pattern as services.html/solutions.html.</t>
+          <t>BUILT 2026-08-12. One-pager built from the 15 partner names + 3 category groupings already in the nav dropdown, using the same real blurbs as the homepage logo wall. Follows the services.html/solutions.html one-pager pattern.</t>
         </is>
       </c>
     </row>
@@ -2377,53 +2369,53 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Blog (proposed)</t>
+          <t>Blog</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>blog.html</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>Missing (High Priority)</t>
+          <t>Blog | aiDataWorks</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Yes — aliases to #insights anchor (shows case studies, not blog content)</t>
+          <t>Yes — Resources dropdown</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes — Resources column</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>The "Blogs" nav item points to the homepage #insights anchor, which shows 4 case-study teasers, not blog content. CANNOT build yet — needs real blog post content from you first.</t>
+          <t>BUILT 2026-08-12. No real blog posts exist yet, so this is an honest "launching soon" page (no fabricated posts) linking to Case Studies in the meantime. Needs real post content before it's more than a landing page.</t>
         </is>
       </c>
     </row>
@@ -2433,53 +2425,53 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Whitepapers (proposed)</t>
+          <t>Whitepapers</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>whitepapers.html</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Missing (High Priority)</t>
+          <t>Whitepapers | aiDataWorks</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Yes — aliases to same #insights anchor as Blogs</t>
+          <t>Yes — Resources dropdown</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes — Resources column</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>Same anchor as Blogs — shows case studies, not whitepapers. No resource library exists. CANNOT build yet — needs whitepaper assets (PDFs) and descriptions from you first.</t>
+          <t>BUILT 2026-08-12. No real whitepapers exist yet, so this is an honest "launching soon" page (no fabricated downloads). Needs real whitepaper assets before it's more than a landing page.</t>
         </is>
       </c>
     </row>
@@ -2489,53 +2481,53 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Newsroom / Press (proposed)</t>
+          <t>Newsroom</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>newsroom.html</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Missing (High Priority)</t>
+          <t>Newsroom | aiDataWorks</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Yes — aliases to same #insights anchor as Blogs</t>
+          <t>Yes — Resources dropdown</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes — Resources column</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>Same anchor as Blogs — shows case studies, not press/news. No newsroom page exists. CANNOT build yet — needs press releases/media mentions/press contact info from you first.</t>
+          <t>BUILT 2026-08-12. Contains the one real announcement already published elsewhere on the site (Salesforce &amp; MuleSoft partner status) plus an honest note that there's no press kit/media contact yet. No fabricated press releases.</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2537,32 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Leadership / Team (proposed)</t>
+          <t>Leadership &amp; Team</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>team.html</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Missing (Medium-High Priority)</t>
+          <t>Leadership &amp; Team | aiDataWorks</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes — About dropdown</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2581,17 +2573,17 @@
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>about.html has a "Who We Are" narrative but zero people — no founder/leadership names, titles, bios, or photos. Credibility gap for a professional-services firm. CANNOT build yet — needs names/titles/bios/headshots from you. Could be a new section on about.html or its own page.</t>
+          <t>BUILT 2026-08-12. No real names/titles/bios/photos exist, so this is an honest page stating that directly and pointing to About + direct contact instead of fabricating bios. Still needs real leadership content from the team to become a real bios page.</t>
         </is>
       </c>
     </row>
@@ -2601,32 +2593,32 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Trust / Security &amp; Compliance (proposed)</t>
+          <t>Trust, Security &amp; Compliance</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>trust.html</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Missing (Medium-High Priority)</t>
+          <t>Trust, Security &amp; Compliance | aiDataWorks</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes — About dropdown</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2637,17 +2629,17 @@
       <c r="I40" s="4" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>Clients are in regulated industries (healthcare/HIPAA, BFSI). Compliance messaging is scattered across an FAQ answer, the Governance section, and one dropdown blurb, with no single reviewable page. CANNOT build yet — needs real security/compliance practices, certifications, and data handling policy from you. Common ask during enterprise security review before a first sales call in these industries.</t>
+          <t>BUILT 2026-08-12. Aggregates the real governance/security claims already published elsewhere (FAQ answer, Solutions Governance domain, Licensing &amp; Reselling compliance advisory) and is explicit that there's no formal trust-center packet (certifications, DPA, sub-processor list) yet. No fabricated compliance claims.</t>
         </is>
       </c>
     </row>
@@ -2657,53 +2649,53 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>404 error page (proposed)</t>
+          <t>404 error page</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>404.html</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Missing (Medium Priority)</t>
+          <t>Page Not Found | aiDataWorks</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No (not a nav page)</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Doesn't exist — a broken/mistyped link currently falls through to a raw server error instead of a branded page with a way back into the site. CAN BUILD NOW — no new content needed, just page chrome + a link home.</t>
+          <t>BUILT 2026-08-12. noindex, links back to Home/Services/Solutions/Case Studies/Contact. GitHub Pages serves root-level 404.html automatically, no extra config needed.</t>
         </is>
       </c>
     </row>
@@ -2713,27 +2705,27 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Missing / Planned</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>robots.txt / sitemap.xml (proposed)</t>
+          <t>robots.txt / sitemap.xml</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>— not built yet</t>
+          <t>robots.txt, sitemap.xml</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Missing (Medium Priority)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2759,7 +2751,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Neither exists — search engines have no crawl guidance and no full list of the site's pages to index. CAN BUILD NOW — no new content needed; sitemap.xml can be generated directly from this sheet's 31 live pages (rows 1-31).</t>
+          <t>BUILT 2026-08-12 via scripts/build_sitemap.py — sitemap.xml is generated directly from the real pages in the repo (35 URLs currently), excluding 404.html and anything noindex, so it can't drift from what's actually published. Re-run the script whenever pages are added/removed.</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2779,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Missing (Medium Priority)</t>
         </is>
@@ -2843,7 +2835,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Missing (Medium Priority)</t>
         </is>
@@ -3512,7 +3504,7 @@
           <t>Partners logo wall on index.html</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Anchor-only</t>
         </is>
@@ -3578,7 +3570,7 @@
           <t>Insights section on index.html</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Anchor-only</t>
         </is>
@@ -3644,7 +3636,7 @@
           <t>FAQ section on index.html</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Anchor-only</t>
         </is>
@@ -3710,7 +3702,7 @@
           <t>Insights section on index.html</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Aliased</t>
         </is>
@@ -3745,7 +3737,7 @@
           <t>Insights section on index.html</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Aliased</t>
         </is>
@@ -3955,7 +3947,7 @@
           <t>Nowhere (placeholder)</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Dead link</t>
         </is>
@@ -4435,7 +4427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4455,7 +4447,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Concrete, verifiable issues in the current codebase — not yet fixed. (3 prior items — dead footer links, the 6 stale legacy service pages, and index-v1.html — were resolved and removed from this list.)</t>
+          <t>Concrete, verifiable issues in the current codebase — not yet fixed. (5 prior items — dead footer links, the 6 stale legacy service pages, index-v1.html, the LinkedIn placeholder, and the Blog/Whitepapers/Newsroom aliasing — were resolved and removed from this list.)</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4487,7 @@
           <t>11 of 13 case-study detail pages (plus the build template) are missing the &lt;script src="../../site.js"&gt; tag, so the mobile hamburger menu / nav accordion JS never loads on those pages.</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4517,47 +4509,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Footer LinkedIn icon still contains literal placeholder text instead of a real URL: [PLACEHOLDER: real aiDataWorks LinkedIn company URL].</t>
+          <t>No real aiDataWorks LinkedIn company URL exists yet — the footer's LinkedIn icon was removed rather than left as a dead/placeholder link.</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>index.html footer (site-wide via sync)</t>
+          <t>partials/footer.html (site-wide)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Swap in the real aiDataWorks LinkedIn company page URL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Whitepapers and Newsroom nav/footer entries both alias to the homepage #insights anchor, which now shows case-study teasers — not blog, whitepaper, or press content for any of the three nav items that point to it.</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Nav Resources dropdown + footer, site-wide</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>See Page Inventory rows 32-34 (Blog, Whitepapers, Newsroom) — all three need real content from you before they can be built.</t>
+          <t>Once you have the real LinkedIn company page URL, add the icon back to partials/footer.html and run scripts/build_nav.py to restore it everywhere at once.</t>
         </is>
       </c>
     </row>

--- a/aiDataWorks_Site_Page_Tracker.xlsx
+++ b/aiDataWorks_Site_Page_Tracker.xlsx
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Orphaned</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2611,14 +2611,14 @@
           <t>Trust, Security &amp; Compliance | aiDataWorks</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Live</t>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Orphaned</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Yes — About dropdown</t>
+          <t>No — removed from About dropdown (was 6 items, trimmed to 4)</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>BUILT 2026-08-12. Aggregates the real governance/security claims already published elsewhere (FAQ answer, Solutions Governance domain, Licensing &amp; Reselling compliance advisory) and is explicit that there's no formal trust-center packet (certifications, DPA, sub-processor list) yet. No fabricated compliance claims.</t>
+          <t>BUILT 2026-08-12, then UNLINKED 2026-08-12 — removed from the About dropdown (desktop + mobile) to keep it at 4 items max, per request. File still exists with real, honest content, but is no longer reachable from any nav menu. Marked noindex and excluded from sitemap.xml/robots crawl scope. Re-link it (and drop the noindex tag) if it should come back later.</t>
         </is>
       </c>
     </row>
